--- a/P4/qnap/out-i.xlsx
+++ b/P4/qnap/out-i.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hexdhog/Documents/uib/CS/Y2/ACSI/P4/qnap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{963E6087-2F8C-934C-8707-13B82F81065E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2429F47A-4D45-6C46-8F1C-04527654F8FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8180" yWindow="2180" windowWidth="27640" windowHeight="16940" xr2:uid="{96F2D826-A099-6A4F-8BB9-8033B883AADB}"/>
+    <workbookView xWindow="2980" yWindow="3880" windowWidth="28820" windowHeight="17760" xr2:uid="{96F2D826-A099-6A4F-8BB9-8033B883AADB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -254,34 +254,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.38379999999999997</c:v>
+                  <c:v>0.55459999999999998</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.4793</c:v>
+                  <c:v>0.66400000000000003</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.63300000000000001</c:v>
+                  <c:v>0.83399999999999996</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.90800000000000003</c:v>
+                  <c:v>1.1279999999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.4630000000000001</c:v>
+                  <c:v>1.704</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.6579999999999999</c:v>
+                  <c:v>2.9180000000000001</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.8650000000000002</c:v>
+                  <c:v>5.1349999999999998</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>7.734</c:v>
+                  <c:v>8.0060000000000002</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>10.73</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>13.73</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -602,34 +602,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.64700000000000002</c:v>
+                  <c:v>0.85160000000000002</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.966</c:v>
+                  <c:v>2.2250000000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.7300000000000004</c:v>
+                  <c:v>5.0019999999999998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.7279999999999998</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10.73</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>13.73</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>16.73</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>19.73</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>22.73</c:v>
+                  <c:v>23</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>25.73</c:v>
+                  <c:v>26</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2315,7 +2315,7 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>0.38379999999999997</v>
+        <v>0.55459999999999998</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -2323,7 +2323,7 @@
         <v>20</v>
       </c>
       <c r="B4" s="1">
-        <v>0.4793</v>
+        <v>0.66400000000000003</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -2331,7 +2331,7 @@
         <v>30</v>
       </c>
       <c r="B5" s="1">
-        <v>0.63300000000000001</v>
+        <v>0.83399999999999996</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -2339,7 +2339,7 @@
         <v>40</v>
       </c>
       <c r="B6" s="1">
-        <v>0.90800000000000003</v>
+        <v>1.1279999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -2347,7 +2347,7 @@
         <v>50</v>
       </c>
       <c r="B7" s="1">
-        <v>1.4630000000000001</v>
+        <v>1.704</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -2355,7 +2355,7 @@
         <v>60</v>
       </c>
       <c r="B8" s="1">
-        <v>2.6579999999999999</v>
+        <v>2.9180000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -2363,7 +2363,7 @@
         <v>70</v>
       </c>
       <c r="B9" s="1">
-        <v>4.8650000000000002</v>
+        <v>5.1349999999999998</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -2371,7 +2371,7 @@
         <v>80</v>
       </c>
       <c r="B10" s="1">
-        <v>7.734</v>
+        <v>8.0060000000000002</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -2379,7 +2379,7 @@
         <v>90</v>
       </c>
       <c r="B11" s="1">
-        <v>10.73</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
@@ -2387,7 +2387,7 @@
         <v>100</v>
       </c>
       <c r="B12" s="1">
-        <v>13.73</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
@@ -2408,7 +2408,7 @@
         <v>10</v>
       </c>
       <c r="B25" s="2">
-        <v>0.64700000000000002</v>
+        <v>0.85160000000000002</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
@@ -2416,7 +2416,7 @@
         <v>20</v>
       </c>
       <c r="B26" s="2">
-        <v>1.966</v>
+        <v>2.2250000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
@@ -2424,7 +2424,7 @@
         <v>30</v>
       </c>
       <c r="B27" s="2">
-        <v>4.7300000000000004</v>
+        <v>5.0019999999999998</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
@@ -2432,7 +2432,7 @@
         <v>40</v>
       </c>
       <c r="B28" s="2">
-        <v>7.7279999999999998</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
@@ -2440,7 +2440,7 @@
         <v>50</v>
       </c>
       <c r="B29" s="2">
-        <v>10.73</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
@@ -2448,7 +2448,7 @@
         <v>60</v>
       </c>
       <c r="B30" s="2">
-        <v>13.73</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
@@ -2456,7 +2456,7 @@
         <v>70</v>
       </c>
       <c r="B31" s="2">
-        <v>16.73</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
@@ -2464,7 +2464,7 @@
         <v>80</v>
       </c>
       <c r="B32" s="2">
-        <v>19.73</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
@@ -2472,7 +2472,7 @@
         <v>90</v>
       </c>
       <c r="B33" s="2">
-        <v>22.73</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
@@ -2480,7 +2480,7 @@
         <v>100</v>
       </c>
       <c r="B34" s="2">
-        <v>25.73</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
